--- a/Project Outputs for Powerboard_SAUVC26/Assembly 01/Документация/ГИДР.123456.015-01.01 ПЭ3.xlsx
+++ b/Project Outputs for Powerboard_SAUVC26/Assembly 01/Документация/ГИДР.123456.015-01.01 ПЭ3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\AppData\Local\TempReleases\Snapshot\2\Assembly 01\Документация\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\AppData\Local\TempReleases\Snapshot\1\Assembly 01\Документация\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABB02805-AF54-4306-87FF-795ED0EB2A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{75FA690F-661B-496F-A011-451BC5201B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7ED908DA-52EB-4B27-933C-610DF01B5554}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{95AF640D-7AD7-4364-BD30-A8771B4A4C2C}"/>
   </bookViews>
   <sheets>
     <sheet name="ГИДР.123456.015-01.01 ПЭ3" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
   <si>
     <t>Line #</t>
   </si>
@@ -174,6 +174,18 @@
     <t>VD3_1, VD3_2, VD3_3, VD3_4, VD3_5, VD4_1, VD4_2, VD4_3, VD4_4, VD4_5</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>SMBJ16A</t>
+  </si>
+  <si>
+    <t>Защитный диод на 16 В, рассеиваемая мощность 600 Вт</t>
+  </si>
+  <si>
+    <t>VD1_1, VD1_2, VD1_3, VD1_4, VD1_5, VD2_1, VD2_2, VD2_3, VD2_4, VD2_5</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
@@ -183,7 +195,7 @@
     <t>Защитный диод на 24 В, рассеиваемая мощность 600 Вт</t>
   </si>
   <si>
-    <t>VD1_1, VD1_2, VD1_3, VD1_4, VD1_5, VD2_1, VD2_2, VD2_3, VD2_4, VD2_5, VD5</t>
+    <t>VD5</t>
   </si>
   <si>
     <t>5</t>
@@ -243,7 +255,7 @@
     <t>Резистор номиналом 2,2 кОм и точностью 1%</t>
   </si>
   <si>
-    <t>R7, R8</t>
+    <t>R9, R10</t>
   </si>
   <si>
     <t>17</t>
@@ -252,7 +264,13 @@
     <t>Резистор номиналом 10 кОм и точностью 1%</t>
   </si>
   <si>
-    <t>R5, R6, R9, R10, R11</t>
+    <t>R7, R8, R11, R12, R13</t>
+  </si>
+  <si>
+    <t>Резистор номиналом 15 Ом 1%</t>
+  </si>
+  <si>
+    <t>R1_1, R1_2, R1_3, R1_4, R1_5, R2_1, R2_2, R2_3, R2_4, R2_5</t>
   </si>
   <si>
     <t>18</t>
@@ -261,7 +279,7 @@
     <t>Резистор номиналом 33 кОм и точностью 1%</t>
   </si>
   <si>
-    <t>R1, R2, R3, R4</t>
+    <t>R3, R4, R5, R6</t>
   </si>
   <si>
     <t>12</t>
@@ -677,8 +695,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F403B04-21AC-48E5-AA36-6B8ECA91714E}">
-  <dimension ref="A1:L22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6520EB7-88BD-46BE-AC96-2FCFA0B281D6}">
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -963,7 +981,7 @@
         <v>51</v>
       </c>
       <c r="E11" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -987,7 +1005,7 @@
         <v>55</v>
       </c>
       <c r="E12" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1011,7 +1029,7 @@
         <v>59</v>
       </c>
       <c r="E13" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1059,7 +1077,7 @@
         <v>67</v>
       </c>
       <c r="E15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1098,16 +1116,16 @@
         <v>72</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E17" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -1119,19 +1137,19 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1143,19 +1161,19 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="E19" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1167,19 +1185,19 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="E20" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1191,19 +1209,19 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="E21" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1215,16 +1233,16 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -1237,6 +1255,54 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
     </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Project Outputs for Powerboard_SAUVC26/Assembly 01/Документация/ГИДР.123456.015-01.01 ПЭ3.xlsx
+++ b/Project Outputs for Powerboard_SAUVC26/Assembly 01/Документация/ГИДР.123456.015-01.01 ПЭ3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\AppData\Local\TempReleases\Snapshot\1\Assembly 01\Документация\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75FA690F-661B-496F-A011-451BC5201B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D428B629-D8DF-4D6B-97CB-03A8699DE97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{95AF640D-7AD7-4364-BD30-A8771B4A4C2C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5ACBBD4C-C42A-4AA3-B665-C732D1FF7C2E}"/>
   </bookViews>
   <sheets>
     <sheet name="ГИДР.123456.015-01.01 ПЭ3" sheetId="1" r:id="rId1"/>
@@ -695,7 +695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6520EB7-88BD-46BE-AC96-2FCFA0B281D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0BD7319-AE77-43E7-97D3-B3EFDEC0328B}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>

--- a/Project Outputs for Powerboard_SAUVC26/Assembly 01/Документация/ГИДР.123456.015-01.01 ПЭ3.xlsx
+++ b/Project Outputs for Powerboard_SAUVC26/Assembly 01/Документация/ГИДР.123456.015-01.01 ПЭ3.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\AppData\Local\TempReleases\Snapshot\1\Assembly 01\Документация\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D428B629-D8DF-4D6B-97CB-03A8699DE97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2C3E68D-A371-43B0-BBB0-37FDF0AD7EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5ACBBD4C-C42A-4AA3-B665-C732D1FF7C2E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{851CD7DE-0A63-46FB-AFEC-68D3E3E060A9}"/>
   </bookViews>
   <sheets>
     <sheet name="ГИДР.123456.015-01.01 ПЭ3" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'ГИДР.123456.015-01.01 ПЭ3'!$1:$1</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -695,7 +692,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0BD7319-AE77-43E7-97D3-B3EFDEC0328B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75974DFD-60AA-45E9-AA0E-958116240DF6}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1305,6 +1302,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Project Outputs for Powerboard_SAUVC26/Assembly 01/Документация/ГИДР.123456.015-01.01 ПЭ3.xlsx
+++ b/Project Outputs for Powerboard_SAUVC26/Assembly 01/Документация/ГИДР.123456.015-01.01 ПЭ3.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\AppData\Local\TempReleases\Snapshot\1\Assembly 01\Документация\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2C3E68D-A371-43B0-BBB0-37FDF0AD7EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3D81BA3-C422-4909-B16A-58CE6B696FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{851CD7DE-0A63-46FB-AFEC-68D3E3E060A9}"/>
+    <workbookView xWindow="4932" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{8F0CCEC8-113C-4C9A-B14E-46073AE20192}"/>
   </bookViews>
   <sheets>
     <sheet name="ГИДР.123456.015-01.01 ПЭ3" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'ГИДР.123456.015-01.01 ПЭ3'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="91">
   <si>
     <t>Line #</t>
   </si>
@@ -111,30 +114,18 @@
     <t>VT1_1, VT1_2, VT1_3, VT1_4, VT1_5, VT2_1, VT2_2, VT2_3, VT2_4, VT2_5</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>IPD90P04P405</t>
-  </si>
-  <si>
-    <t>P-канальный MOSFET</t>
+    <t/>
+  </si>
+  <si>
+    <t>IRF9310TR</t>
+  </si>
+  <si>
+    <t>P-канальный MOSFET, 30 В, 20 А</t>
   </si>
   <si>
     <t>VT5, VT6</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>BC857</t>
-  </si>
-  <si>
-    <t>Биполярный транзистор PNP 45В 0.1А 0.25Вт</t>
-  </si>
-  <si>
-    <t>VT3, VT4, VT7, VT8</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -171,28 +162,13 @@
     <t>VD3_1, VD3_2, VD3_3, VD3_4, VD3_5, VD4_1, VD4_2, VD4_3, VD4_4, VD4_5</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>SMBJ16A</t>
   </si>
   <si>
     <t>Защитный диод на 16 В, рассеиваемая мощность 600 Вт</t>
   </si>
   <si>
-    <t>VD1_1, VD1_2, VD1_3, VD1_4, VD1_5, VD2_1, VD2_2, VD2_3, VD2_4, VD2_5</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>SMBJ24A</t>
-  </si>
-  <si>
-    <t>Защитный диод на 24 В, рассеиваемая мощность 600 Вт</t>
-  </si>
-  <si>
-    <t>VD5</t>
+    <t>VD1_1, VD1_2, VD1_3, VD1_4, VD1_5, VD2_1, VD2_2, VD2_3, VD2_4, VD2_5, VD5</t>
   </si>
   <si>
     <t>5</t>
@@ -277,6 +253,15 @@
   </si>
   <si>
     <t>R3, R4, R5, R6</t>
+  </si>
+  <si>
+    <t>BC857BS</t>
+  </si>
+  <si>
+    <t>Сборка из биполярных транзисторов, 2 pnp, 45 В,  0.1А</t>
+  </si>
+  <si>
+    <t>VT3, VT4</t>
   </si>
   <si>
     <t>12</t>
@@ -692,8 +677,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75974DFD-60AA-45E9-AA0E-958116240DF6}">
-  <dimension ref="A1:L24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC85B18F-0AFC-415F-8F48-6B0966E839A6}">
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -882,7 +867,7 @@
         <v>35</v>
       </c>
       <c r="E7" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -906,7 +891,7 @@
         <v>39</v>
       </c>
       <c r="E8" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -930,7 +915,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -942,19 +927,19 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="E10" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -966,19 +951,19 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="E11" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -990,16 +975,16 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -1014,19 +999,19 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="E13" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1038,19 +1023,19 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="E14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1062,19 +1047,19 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="E15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1086,19 +1071,19 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="E16" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1110,19 +1095,19 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E17" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -1134,19 +1119,19 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E18" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1158,19 +1143,19 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E19" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1182,16 +1167,16 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="E20" s="1">
         <v>4</v>
@@ -1206,19 +1191,19 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="E21" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1230,16 +1215,16 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -1254,16 +1239,16 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -1276,31 +1261,8 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>